--- a/tools/excel_export/excel/player_levels.xlsx
+++ b/tools/excel_export/excel/player_levels.xlsx
@@ -519,7 +519,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E103"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -605,7 +605,7 @@
         <v>120</v>
       </c>
       <c r="C5" s="4">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
@@ -618,7 +618,7 @@
         <v>140</v>
       </c>
       <c r="C6" s="4">
-        <v>180</v>
+        <v>50</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>15</v>
@@ -635,7 +635,7 @@
         <v>170</v>
       </c>
       <c r="C7" s="4">
-        <v>240</v>
+        <v>70</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
@@ -648,7 +648,7 @@
         <v>210</v>
       </c>
       <c r="C8" s="4">
-        <v>300</v>
+        <v>80</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>17</v>
@@ -665,7 +665,7 @@
         <v>250</v>
       </c>
       <c r="C9" s="4">
-        <v>360</v>
+        <v>100</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
@@ -678,7 +678,7 @@
         <v>300</v>
       </c>
       <c r="C10" s="4">
-        <v>420</v>
+        <v>120</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -691,7 +691,7 @@
         <v>360</v>
       </c>
       <c r="C11" s="4">
-        <v>480</v>
+        <v>130</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
@@ -704,7 +704,7 @@
         <v>430</v>
       </c>
       <c r="C12" s="4">
-        <v>540</v>
+        <v>150</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
@@ -717,7 +717,7 @@
         <v>520</v>
       </c>
       <c r="C13" s="4">
-        <v>600</v>
+        <v>170</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
@@ -730,7 +730,7 @@
         <v>620</v>
       </c>
       <c r="C14" s="4">
-        <v>660</v>
+        <v>180</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
@@ -740,10 +740,10 @@
         <v>12</v>
       </c>
       <c r="B15" s="4">
-        <v>740</v>
+        <v>720</v>
       </c>
       <c r="C15" s="4">
-        <v>720</v>
+        <v>200</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
@@ -753,10 +753,10 @@
         <v>13</v>
       </c>
       <c r="B16" s="4">
-        <v>890</v>
+        <v>820</v>
       </c>
       <c r="C16" s="4">
-        <v>780</v>
+        <v>210</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
@@ -766,10 +766,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="4">
-        <v>1070</v>
+        <v>920</v>
       </c>
       <c r="C17" s="4">
-        <v>840</v>
+        <v>230</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
@@ -779,10 +779,10 @@
         <v>15</v>
       </c>
       <c r="B18" s="4">
-        <v>1280</v>
+        <v>1020</v>
       </c>
       <c r="C18" s="4">
-        <v>900</v>
+        <v>250</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>19</v>
@@ -796,10 +796,10 @@
         <v>16</v>
       </c>
       <c r="B19" s="4">
-        <v>1540</v>
+        <v>1120</v>
       </c>
       <c r="C19" s="4">
-        <v>960</v>
+        <v>260</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
@@ -809,10 +809,10 @@
         <v>17</v>
       </c>
       <c r="B20" s="4">
-        <v>1850</v>
+        <v>1220</v>
       </c>
       <c r="C20" s="4">
-        <v>1020</v>
+        <v>280</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
@@ -822,10 +822,10 @@
         <v>18</v>
       </c>
       <c r="B21" s="4">
-        <v>2220</v>
+        <v>1320</v>
       </c>
       <c r="C21" s="4">
-        <v>1080</v>
+        <v>300</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
@@ -835,10 +835,10 @@
         <v>19</v>
       </c>
       <c r="B22" s="4">
-        <v>2660</v>
+        <v>1420</v>
       </c>
       <c r="C22" s="4">
-        <v>1140</v>
+        <v>310</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
@@ -848,10 +848,10 @@
         <v>20</v>
       </c>
       <c r="B23" s="4">
-        <v>3190</v>
+        <v>1520</v>
       </c>
       <c r="C23" s="4">
-        <v>1200</v>
+        <v>330</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
@@ -861,10 +861,10 @@
         <v>21</v>
       </c>
       <c r="B24" s="4">
-        <v>3830</v>
+        <v>1620</v>
       </c>
       <c r="C24" s="4">
-        <v>1260</v>
+        <v>350</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
@@ -874,10 +874,10 @@
         <v>22</v>
       </c>
       <c r="B25" s="4">
-        <v>4600</v>
+        <v>1720</v>
       </c>
       <c r="C25" s="4">
-        <v>1320</v>
+        <v>360</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
@@ -887,10 +887,10 @@
         <v>23</v>
       </c>
       <c r="B26" s="4">
-        <v>5520</v>
+        <v>1820</v>
       </c>
       <c r="C26" s="4">
-        <v>1380</v>
+        <v>380</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
@@ -900,10 +900,10 @@
         <v>24</v>
       </c>
       <c r="B27" s="4">
-        <v>6620</v>
+        <v>1920</v>
       </c>
       <c r="C27" s="4">
-        <v>1440</v>
+        <v>400</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
@@ -913,10 +913,10 @@
         <v>25</v>
       </c>
       <c r="B28" s="4">
-        <v>7950</v>
+        <v>2020</v>
       </c>
       <c r="C28" s="4">
-        <v>1500</v>
+        <v>410</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
@@ -926,10 +926,10 @@
         <v>26</v>
       </c>
       <c r="B29" s="4">
-        <v>9540</v>
+        <v>2120</v>
       </c>
       <c r="C29" s="4">
-        <v>1560</v>
+        <v>430</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
@@ -939,10 +939,10 @@
         <v>27</v>
       </c>
       <c r="B30" s="4">
-        <v>11450</v>
+        <v>2220</v>
       </c>
       <c r="C30" s="4">
-        <v>1620</v>
+        <v>450</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
@@ -952,10 +952,10 @@
         <v>28</v>
       </c>
       <c r="B31" s="4">
-        <v>13740</v>
+        <v>2320</v>
       </c>
       <c r="C31" s="4">
-        <v>1680</v>
+        <v>460</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
@@ -965,10 +965,10 @@
         <v>29</v>
       </c>
       <c r="B32" s="4">
-        <v>16480</v>
+        <v>2420</v>
       </c>
       <c r="C32" s="4">
-        <v>1740</v>
+        <v>480</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
@@ -978,15 +978,925 @@
         <v>30</v>
       </c>
       <c r="B33" s="4">
+        <v>2520</v>
+      </c>
+      <c r="C33" s="4">
+        <v>800</v>
+      </c>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="4">
+        <v>31</v>
+      </c>
+      <c r="B34" s="4">
+        <v>2620</v>
+      </c>
+      <c r="C34" s="4">
+        <v>120</v>
+      </c>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="4">
+        <v>32</v>
+      </c>
+      <c r="B35" s="4">
+        <v>2720</v>
+      </c>
+      <c r="C35" s="4">
+        <v>120</v>
+      </c>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="4">
+        <v>33</v>
+      </c>
+      <c r="B36" s="4">
+        <v>2820</v>
+      </c>
+      <c r="C36" s="4">
+        <v>120</v>
+      </c>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="4">
+        <v>34</v>
+      </c>
+      <c r="B37" s="4">
+        <v>2920</v>
+      </c>
+      <c r="C37" s="4">
+        <v>120</v>
+      </c>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="4">
+        <v>35</v>
+      </c>
+      <c r="B38" s="4">
+        <v>3020</v>
+      </c>
+      <c r="C38" s="4">
+        <v>120</v>
+      </c>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="4">
+        <v>36</v>
+      </c>
+      <c r="B39" s="4">
+        <v>3120</v>
+      </c>
+      <c r="C39" s="4">
+        <v>120</v>
+      </c>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="4">
+        <v>37</v>
+      </c>
+      <c r="B40" s="4">
+        <v>3220</v>
+      </c>
+      <c r="C40" s="4">
+        <v>120</v>
+      </c>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="4">
+        <v>38</v>
+      </c>
+      <c r="B41" s="4">
+        <v>3320</v>
+      </c>
+      <c r="C41" s="4">
+        <v>120</v>
+      </c>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="4">
+        <v>39</v>
+      </c>
+      <c r="B42" s="4">
+        <v>3420</v>
+      </c>
+      <c r="C42" s="4">
+        <v>120</v>
+      </c>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="4">
+        <v>40</v>
+      </c>
+      <c r="B43" s="4">
+        <v>3520</v>
+      </c>
+      <c r="C43" s="4">
+        <v>300</v>
+      </c>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="4">
+        <v>41</v>
+      </c>
+      <c r="B44" s="4">
+        <v>3620</v>
+      </c>
+      <c r="C44" s="4">
+        <v>120</v>
+      </c>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="4">
+        <v>42</v>
+      </c>
+      <c r="B45" s="4">
+        <v>3720</v>
+      </c>
+      <c r="C45" s="4">
+        <v>120</v>
+      </c>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="4">
+        <v>43</v>
+      </c>
+      <c r="B46" s="4">
+        <v>3820</v>
+      </c>
+      <c r="C46" s="4">
+        <v>120</v>
+      </c>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="4">
+        <v>44</v>
+      </c>
+      <c r="B47" s="4">
+        <v>3920</v>
+      </c>
+      <c r="C47" s="4">
+        <v>120</v>
+      </c>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="4">
+        <v>45</v>
+      </c>
+      <c r="B48" s="4">
+        <v>4020</v>
+      </c>
+      <c r="C48" s="4">
+        <v>120</v>
+      </c>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="4">
+        <v>46</v>
+      </c>
+      <c r="B49" s="4">
+        <v>4120</v>
+      </c>
+      <c r="C49" s="4">
+        <v>120</v>
+      </c>
+      <c r="D49" s="4"/>
+      <c r="E49" s="4"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="4">
+        <v>47</v>
+      </c>
+      <c r="B50" s="4">
+        <v>4220</v>
+      </c>
+      <c r="C50" s="4">
+        <v>120</v>
+      </c>
+      <c r="D50" s="4"/>
+      <c r="E50" s="4"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="4">
+        <v>48</v>
+      </c>
+      <c r="B51" s="4">
+        <v>4320</v>
+      </c>
+      <c r="C51" s="4">
+        <v>120</v>
+      </c>
+      <c r="D51" s="4"/>
+      <c r="E51" s="4"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="4">
+        <v>49</v>
+      </c>
+      <c r="B52" s="4">
+        <v>4420</v>
+      </c>
+      <c r="C52" s="4">
+        <v>120</v>
+      </c>
+      <c r="D52" s="4"/>
+      <c r="E52" s="4"/>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="4">
+        <v>50</v>
+      </c>
+      <c r="B53" s="4">
+        <v>4520</v>
+      </c>
+      <c r="C53" s="4">
+        <v>300</v>
+      </c>
+      <c r="D53" s="4"/>
+      <c r="E53" s="4"/>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="4">
+        <v>51</v>
+      </c>
+      <c r="B54" s="4">
+        <v>4620</v>
+      </c>
+      <c r="C54" s="4">
+        <v>120</v>
+      </c>
+      <c r="D54" s="4"/>
+      <c r="E54" s="4"/>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="4">
+        <v>52</v>
+      </c>
+      <c r="B55" s="4">
+        <v>4720</v>
+      </c>
+      <c r="C55" s="4">
+        <v>120</v>
+      </c>
+      <c r="D55" s="4"/>
+      <c r="E55" s="4"/>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="4">
+        <v>53</v>
+      </c>
+      <c r="B56" s="4">
+        <v>4820</v>
+      </c>
+      <c r="C56" s="4">
+        <v>120</v>
+      </c>
+      <c r="D56" s="4"/>
+      <c r="E56" s="4"/>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="4">
+        <v>54</v>
+      </c>
+      <c r="B57" s="4">
+        <v>4920</v>
+      </c>
+      <c r="C57" s="4">
+        <v>120</v>
+      </c>
+      <c r="D57" s="4"/>
+      <c r="E57" s="4"/>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="4">
+        <v>55</v>
+      </c>
+      <c r="B58" s="4">
+        <v>5020</v>
+      </c>
+      <c r="C58" s="4">
+        <v>120</v>
+      </c>
+      <c r="D58" s="4"/>
+      <c r="E58" s="4"/>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="4">
+        <v>56</v>
+      </c>
+      <c r="B59" s="4">
+        <v>5120</v>
+      </c>
+      <c r="C59" s="4">
+        <v>120</v>
+      </c>
+      <c r="D59" s="4"/>
+      <c r="E59" s="4"/>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="4">
+        <v>57</v>
+      </c>
+      <c r="B60" s="4">
+        <v>5220</v>
+      </c>
+      <c r="C60" s="4">
+        <v>120</v>
+      </c>
+      <c r="D60" s="4"/>
+      <c r="E60" s="4"/>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="4">
+        <v>58</v>
+      </c>
+      <c r="B61" s="4">
+        <v>5320</v>
+      </c>
+      <c r="C61" s="4">
+        <v>120</v>
+      </c>
+      <c r="D61" s="4"/>
+      <c r="E61" s="4"/>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="4">
+        <v>59</v>
+      </c>
+      <c r="B62" s="4">
+        <v>5420</v>
+      </c>
+      <c r="C62" s="4">
+        <v>120</v>
+      </c>
+      <c r="D62" s="4"/>
+      <c r="E62" s="4"/>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="4">
+        <v>60</v>
+      </c>
+      <c r="B63" s="4">
+        <v>5520</v>
+      </c>
+      <c r="C63" s="4">
+        <v>300</v>
+      </c>
+      <c r="D63" s="4"/>
+      <c r="E63" s="4"/>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="4">
+        <v>61</v>
+      </c>
+      <c r="B64" s="4">
+        <v>5620</v>
+      </c>
+      <c r="C64" s="4">
+        <v>120</v>
+      </c>
+      <c r="D64" s="4"/>
+      <c r="E64" s="4"/>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="4">
+        <v>62</v>
+      </c>
+      <c r="B65" s="4">
+        <v>5720</v>
+      </c>
+      <c r="C65" s="4">
+        <v>120</v>
+      </c>
+      <c r="D65" s="4"/>
+      <c r="E65" s="4"/>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="4">
+        <v>63</v>
+      </c>
+      <c r="B66" s="4">
+        <v>5820</v>
+      </c>
+      <c r="C66" s="4">
+        <v>120</v>
+      </c>
+      <c r="D66" s="4"/>
+      <c r="E66" s="4"/>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="4">
+        <v>64</v>
+      </c>
+      <c r="B67" s="4">
+        <v>5920</v>
+      </c>
+      <c r="C67" s="4">
+        <v>120</v>
+      </c>
+      <c r="D67" s="4"/>
+      <c r="E67" s="4"/>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="4">
+        <v>65</v>
+      </c>
+      <c r="B68" s="4">
+        <v>6020</v>
+      </c>
+      <c r="C68" s="4">
+        <v>120</v>
+      </c>
+      <c r="D68" s="4"/>
+      <c r="E68" s="4"/>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="4">
+        <v>66</v>
+      </c>
+      <c r="B69" s="4">
+        <v>6120</v>
+      </c>
+      <c r="C69" s="4">
+        <v>120</v>
+      </c>
+      <c r="D69" s="4"/>
+      <c r="E69" s="4"/>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="4">
+        <v>67</v>
+      </c>
+      <c r="B70" s="4">
+        <v>6220</v>
+      </c>
+      <c r="C70" s="4">
+        <v>120</v>
+      </c>
+      <c r="D70" s="4"/>
+      <c r="E70" s="4"/>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="4">
+        <v>68</v>
+      </c>
+      <c r="B71" s="4">
+        <v>6320</v>
+      </c>
+      <c r="C71" s="4">
+        <v>120</v>
+      </c>
+      <c r="D71" s="4"/>
+      <c r="E71" s="4"/>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="4">
+        <v>69</v>
+      </c>
+      <c r="B72" s="4">
+        <v>6420</v>
+      </c>
+      <c r="C72" s="4">
+        <v>120</v>
+      </c>
+      <c r="D72" s="4"/>
+      <c r="E72" s="4"/>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="4">
+        <v>70</v>
+      </c>
+      <c r="B73" s="4">
+        <v>6520</v>
+      </c>
+      <c r="C73" s="4">
+        <v>300</v>
+      </c>
+      <c r="D73" s="4"/>
+      <c r="E73" s="4"/>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="4">
+        <v>71</v>
+      </c>
+      <c r="B74" s="4">
+        <v>6620</v>
+      </c>
+      <c r="C74" s="4">
+        <v>120</v>
+      </c>
+      <c r="D74" s="4"/>
+      <c r="E74" s="4"/>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="4">
+        <v>72</v>
+      </c>
+      <c r="B75" s="4">
+        <v>6720</v>
+      </c>
+      <c r="C75" s="4">
+        <v>120</v>
+      </c>
+      <c r="D75" s="4"/>
+      <c r="E75" s="4"/>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="4">
+        <v>73</v>
+      </c>
+      <c r="B76" s="4">
+        <v>6820</v>
+      </c>
+      <c r="C76" s="4">
+        <v>120</v>
+      </c>
+      <c r="D76" s="4"/>
+      <c r="E76" s="4"/>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="4">
+        <v>74</v>
+      </c>
+      <c r="B77" s="4">
+        <v>6920</v>
+      </c>
+      <c r="C77" s="4">
+        <v>120</v>
+      </c>
+      <c r="D77" s="4"/>
+      <c r="E77" s="4"/>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="4">
+        <v>75</v>
+      </c>
+      <c r="B78" s="4">
+        <v>7020</v>
+      </c>
+      <c r="C78" s="4">
+        <v>120</v>
+      </c>
+      <c r="D78" s="4"/>
+      <c r="E78" s="4"/>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="4">
+        <v>76</v>
+      </c>
+      <c r="B79" s="4">
+        <v>7120</v>
+      </c>
+      <c r="C79" s="4">
+        <v>120</v>
+      </c>
+      <c r="D79" s="4"/>
+      <c r="E79" s="4"/>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="4">
+        <v>77</v>
+      </c>
+      <c r="B80" s="4">
+        <v>7220</v>
+      </c>
+      <c r="C80" s="4">
+        <v>120</v>
+      </c>
+      <c r="D80" s="4"/>
+      <c r="E80" s="4"/>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="4">
+        <v>78</v>
+      </c>
+      <c r="B81" s="4">
+        <v>7320</v>
+      </c>
+      <c r="C81" s="4">
+        <v>120</v>
+      </c>
+      <c r="D81" s="4"/>
+      <c r="E81" s="4"/>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="4">
+        <v>79</v>
+      </c>
+      <c r="B82" s="4">
+        <v>7420</v>
+      </c>
+      <c r="C82" s="4">
+        <v>120</v>
+      </c>
+      <c r="D82" s="4"/>
+      <c r="E82" s="4"/>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="4">
+        <v>80</v>
+      </c>
+      <c r="B83" s="4">
+        <v>7520</v>
+      </c>
+      <c r="C83" s="4">
+        <v>300</v>
+      </c>
+      <c r="D83" s="4"/>
+      <c r="E83" s="4"/>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="4">
+        <v>81</v>
+      </c>
+      <c r="B84" s="4">
+        <v>7620</v>
+      </c>
+      <c r="C84" s="4">
+        <v>120</v>
+      </c>
+      <c r="D84" s="4"/>
+      <c r="E84" s="4"/>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="4">
+        <v>82</v>
+      </c>
+      <c r="B85" s="4">
+        <v>7720</v>
+      </c>
+      <c r="C85" s="4">
+        <v>120</v>
+      </c>
+      <c r="D85" s="4"/>
+      <c r="E85" s="4"/>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="4">
+        <v>83</v>
+      </c>
+      <c r="B86" s="4">
+        <v>7820</v>
+      </c>
+      <c r="C86" s="4">
+        <v>120</v>
+      </c>
+      <c r="D86" s="4"/>
+      <c r="E86" s="4"/>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="4">
+        <v>84</v>
+      </c>
+      <c r="B87" s="4">
+        <v>7920</v>
+      </c>
+      <c r="C87" s="4">
+        <v>120</v>
+      </c>
+      <c r="D87" s="4"/>
+      <c r="E87" s="4"/>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="4">
+        <v>85</v>
+      </c>
+      <c r="B88" s="4">
+        <v>8020</v>
+      </c>
+      <c r="C88" s="4">
+        <v>120</v>
+      </c>
+      <c r="D88" s="4"/>
+      <c r="E88" s="4"/>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="4">
+        <v>86</v>
+      </c>
+      <c r="B89" s="4">
+        <v>8120</v>
+      </c>
+      <c r="C89" s="4">
+        <v>120</v>
+      </c>
+      <c r="D89" s="4"/>
+      <c r="E89" s="4"/>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="4">
+        <v>87</v>
+      </c>
+      <c r="B90" s="4">
+        <v>8220</v>
+      </c>
+      <c r="C90" s="4">
+        <v>120</v>
+      </c>
+      <c r="D90" s="4"/>
+      <c r="E90" s="4"/>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="4">
+        <v>88</v>
+      </c>
+      <c r="B91" s="4">
+        <v>8320</v>
+      </c>
+      <c r="C91" s="4">
+        <v>120</v>
+      </c>
+      <c r="D91" s="4"/>
+      <c r="E91" s="4"/>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="4">
+        <v>89</v>
+      </c>
+      <c r="B92" s="4">
+        <v>8420</v>
+      </c>
+      <c r="C92" s="4">
+        <v>120</v>
+      </c>
+      <c r="D92" s="4"/>
+      <c r="E92" s="4"/>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="4">
+        <v>90</v>
+      </c>
+      <c r="B93" s="4">
+        <v>8520</v>
+      </c>
+      <c r="C93" s="4">
+        <v>300</v>
+      </c>
+      <c r="D93" s="4"/>
+      <c r="E93" s="4"/>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="4">
+        <v>91</v>
+      </c>
+      <c r="B94" s="4">
+        <v>8620</v>
+      </c>
+      <c r="C94" s="4">
+        <v>120</v>
+      </c>
+      <c r="D94" s="4"/>
+      <c r="E94" s="4"/>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="4">
+        <v>92</v>
+      </c>
+      <c r="B95" s="4">
+        <v>8720</v>
+      </c>
+      <c r="C95" s="4">
+        <v>120</v>
+      </c>
+      <c r="D95" s="4"/>
+      <c r="E95" s="4"/>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="4">
+        <v>93</v>
+      </c>
+      <c r="B96" s="4">
+        <v>8820</v>
+      </c>
+      <c r="C96" s="4">
+        <v>120</v>
+      </c>
+      <c r="D96" s="4"/>
+      <c r="E96" s="4"/>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="4">
+        <v>94</v>
+      </c>
+      <c r="B97" s="4">
+        <v>8920</v>
+      </c>
+      <c r="C97" s="4">
+        <v>120</v>
+      </c>
+      <c r="D97" s="4"/>
+      <c r="E97" s="4"/>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="4">
+        <v>95</v>
+      </c>
+      <c r="B98" s="4">
+        <v>9020</v>
+      </c>
+      <c r="C98" s="4">
+        <v>120</v>
+      </c>
+      <c r="D98" s="4"/>
+      <c r="E98" s="4"/>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="4">
+        <v>96</v>
+      </c>
+      <c r="B99" s="4">
+        <v>9120</v>
+      </c>
+      <c r="C99" s="4">
+        <v>120</v>
+      </c>
+      <c r="D99" s="4"/>
+      <c r="E99" s="4"/>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="4">
+        <v>97</v>
+      </c>
+      <c r="B100" s="4">
+        <v>9220</v>
+      </c>
+      <c r="C100" s="4">
+        <v>120</v>
+      </c>
+      <c r="D100" s="4"/>
+      <c r="E100" s="4"/>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" s="4">
+        <v>98</v>
+      </c>
+      <c r="B101" s="4">
+        <v>9320</v>
+      </c>
+      <c r="C101" s="4">
+        <v>120</v>
+      </c>
+      <c r="D101" s="4"/>
+      <c r="E101" s="4"/>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" s="4">
+        <v>99</v>
+      </c>
+      <c r="B102" s="4">
+        <v>9420</v>
+      </c>
+      <c r="C102" s="4">
+        <v>120</v>
+      </c>
+      <c r="D102" s="4"/>
+      <c r="E102" s="4"/>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" s="4">
+        <v>100</v>
+      </c>
+      <c r="B103" s="4">
         <v>0</v>
       </c>
-      <c r="C33" s="4">
-        <v>3000</v>
-      </c>
-      <c r="D33" s="4" t="s">
+      <c r="C103" s="4">
+        <v>800</v>
+      </c>
+      <c r="D103" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E33" s="4" t="s">
+      <c r="E103" s="4" t="s">
         <v>22</v>
       </c>
     </row>
